--- a/output/yearly_population_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_47_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5532</v>
+        <v>6153</v>
       </c>
       <c r="C2" t="n">
-        <v>11665</v>
+        <v>5946</v>
       </c>
       <c r="D2" t="n">
-        <v>24221</v>
+        <v>23684</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3810</v>
+        <v>3901</v>
       </c>
       <c r="C3" t="n">
-        <v>6929</v>
+        <v>7670</v>
       </c>
       <c r="D3" t="n">
-        <v>13285</v>
+        <v>14198</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2911</v>
+        <v>2994</v>
       </c>
       <c r="C4" t="n">
-        <v>5103</v>
+        <v>6278</v>
       </c>
       <c r="D4" t="n">
-        <v>7033</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1806</v>
+        <v>1921</v>
       </c>
       <c r="C5" t="n">
-        <v>3307</v>
+        <v>4359</v>
       </c>
       <c r="D5" t="n">
-        <v>2616</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>985</v>
+        <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>2315</v>
+        <v>3563</v>
       </c>
       <c r="D6" t="n">
-        <v>1104</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>549</v>
       </c>
       <c r="C7" t="n">
-        <v>1533</v>
+        <v>2574</v>
       </c>
       <c r="D7" t="n">
-        <v>642</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="C8" t="n">
-        <v>854</v>
+        <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>402</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6116</v>
+        <v>7895</v>
       </c>
       <c r="C2" t="n">
-        <v>8701</v>
+        <v>15924</v>
       </c>
       <c r="D2" t="n">
-        <v>22548</v>
+        <v>20485</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3753</v>
+        <v>3963</v>
       </c>
       <c r="C3" t="n">
-        <v>8018</v>
+        <v>6112</v>
       </c>
       <c r="D3" t="n">
-        <v>13879</v>
+        <v>14480</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2859</v>
+        <v>2885</v>
       </c>
       <c r="C4" t="n">
-        <v>5841</v>
+        <v>6788</v>
       </c>
       <c r="D4" t="n">
-        <v>7772</v>
+        <v>7124</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2018</v>
+        <v>2113</v>
       </c>
       <c r="C5" t="n">
-        <v>4100</v>
+        <v>5073</v>
       </c>
       <c r="D5" t="n">
-        <v>3257</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1222</v>
+        <v>1340</v>
       </c>
       <c r="C6" t="n">
-        <v>2726</v>
+        <v>3838</v>
       </c>
       <c r="D6" t="n">
-        <v>1310</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>607</v>
+        <v>714</v>
       </c>
       <c r="C7" t="n">
-        <v>1892</v>
+        <v>2999</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="C8" t="n">
-        <v>1144</v>
+        <v>1811</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>830</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8414</v>
+        <v>8125</v>
       </c>
       <c r="C2" t="n">
-        <v>10168</v>
+        <v>15851</v>
       </c>
       <c r="D2" t="n">
-        <v>25363</v>
+        <v>26543</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3858</v>
+        <v>4434</v>
       </c>
       <c r="C3" t="n">
-        <v>7351</v>
+        <v>8822</v>
       </c>
       <c r="D3" t="n">
-        <v>14078</v>
+        <v>14273</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2757</v>
+        <v>2813</v>
       </c>
       <c r="C4" t="n">
-        <v>6645</v>
+        <v>6302</v>
       </c>
       <c r="D4" t="n">
-        <v>8473</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2100</v>
+        <v>2148</v>
       </c>
       <c r="C5" t="n">
-        <v>4783</v>
+        <v>5610</v>
       </c>
       <c r="D5" t="n">
-        <v>3776</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1493</v>
       </c>
       <c r="C6" t="n">
-        <v>3254</v>
+        <v>4291</v>
       </c>
       <c r="D6" t="n">
-        <v>1560</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>765</v>
+        <v>863</v>
       </c>
       <c r="C7" t="n">
-        <v>2242</v>
+        <v>3289</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="C8" t="n">
-        <v>1432</v>
+        <v>2234</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C9" t="n">
-        <v>804</v>
+        <v>1177</v>
       </c>
       <c r="D9" t="n">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>409</v>
+        <v>511</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7530</v>
+        <v>7528</v>
       </c>
       <c r="C2" t="n">
-        <v>6832</v>
+        <v>11032</v>
       </c>
       <c r="D2" t="n">
-        <v>20628</v>
+        <v>21919</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4847</v>
+        <v>5154</v>
       </c>
       <c r="C3" t="n">
-        <v>10973</v>
+        <v>12840</v>
       </c>
       <c r="D3" t="n">
-        <v>15698</v>
+        <v>15464</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1940</v>
+        <v>1984</v>
       </c>
       <c r="C4" t="n">
-        <v>8355</v>
+        <v>8713</v>
       </c>
       <c r="D4" t="n">
-        <v>8186</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1314</v>
+        <v>1379</v>
       </c>
       <c r="C5" t="n">
-        <v>3188</v>
+        <v>4205</v>
       </c>
       <c r="D5" t="n">
-        <v>2580</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>706</v>
+        <v>797</v>
       </c>
       <c r="C6" t="n">
-        <v>2197</v>
+        <v>3223</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>1403</v>
+        <v>2189</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>787</v>
+        <v>1153</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4455</v>
+        <v>4602</v>
       </c>
       <c r="C2" t="n">
-        <v>3602</v>
+        <v>4718</v>
       </c>
       <c r="D2" t="n">
-        <v>14742</v>
+        <v>15892</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5154</v>
+        <v>5290</v>
       </c>
       <c r="C3" t="n">
-        <v>8269</v>
+        <v>10945</v>
       </c>
       <c r="D3" t="n">
-        <v>15464</v>
+        <v>15424</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2668</v>
+        <v>2733</v>
       </c>
       <c r="C4" t="n">
-        <v>9653</v>
+        <v>10728</v>
       </c>
       <c r="D4" t="n">
-        <v>9248</v>
+        <v>8506</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1473</v>
+        <v>1526</v>
       </c>
       <c r="C5" t="n">
-        <v>5457</v>
+        <v>6093</v>
       </c>
       <c r="D5" t="n">
-        <v>3250</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>933</v>
       </c>
       <c r="C6" t="n">
-        <v>2661</v>
+        <v>3709</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>1751</v>
+        <v>2644</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>1015</v>
+        <v>1473</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>536</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4612</v>
+        <v>4384</v>
       </c>
       <c r="C2" t="n">
-        <v>13709</v>
+        <v>13248</v>
       </c>
       <c r="D2" t="n">
-        <v>18559</v>
+        <v>23099</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4115</v>
+        <v>4213</v>
       </c>
       <c r="C3" t="n">
-        <v>5337</v>
+        <v>7245</v>
       </c>
       <c r="D3" t="n">
-        <v>14296</v>
+        <v>14451</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3208</v>
+        <v>3269</v>
       </c>
       <c r="C4" t="n">
-        <v>8761</v>
+        <v>10606</v>
       </c>
       <c r="D4" t="n">
-        <v>10040</v>
+        <v>9376</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>1792</v>
       </c>
       <c r="C5" t="n">
-        <v>7357</v>
+        <v>8057</v>
       </c>
       <c r="D5" t="n">
-        <v>4130</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1030</v>
+        <v>1074</v>
       </c>
       <c r="C6" t="n">
-        <v>3948</v>
+        <v>4740</v>
       </c>
       <c r="D6" t="n">
-        <v>1297</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="C7" t="n">
-        <v>2168</v>
+        <v>3081</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>1327</v>
+        <v>1945</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>886</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2737</v>
+        <v>2672</v>
       </c>
       <c r="C2" t="n">
-        <v>6280</v>
+        <v>6403</v>
       </c>
       <c r="D2" t="n">
-        <v>12817</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4085</v>
+        <v>4105</v>
       </c>
       <c r="C3" t="n">
-        <v>8046</v>
+        <v>8968</v>
       </c>
       <c r="D3" t="n">
-        <v>14430</v>
+        <v>15026</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3550</v>
+        <v>3580</v>
       </c>
       <c r="C4" t="n">
-        <v>8269</v>
+        <v>10371</v>
       </c>
       <c r="D4" t="n">
-        <v>10664</v>
+        <v>10048</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1828</v>
+        <v>1867</v>
       </c>
       <c r="C5" t="n">
-        <v>8766</v>
+        <v>9910</v>
       </c>
       <c r="D5" t="n">
-        <v>4450</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="C6" t="n">
-        <v>4779</v>
+        <v>5532</v>
       </c>
       <c r="D6" t="n">
-        <v>1267</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>2329</v>
+        <v>3346</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1074</v>
+        <v>1421</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3592</v>
+        <v>3792</v>
       </c>
       <c r="C2" t="n">
-        <v>5262</v>
+        <v>5142</v>
       </c>
       <c r="D2" t="n">
-        <v>15437</v>
+        <v>19348</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2985</v>
+        <v>3037</v>
       </c>
       <c r="C3" t="n">
-        <v>6424</v>
+        <v>7021</v>
       </c>
       <c r="D3" t="n">
-        <v>13240</v>
+        <v>14178</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3327</v>
+        <v>3307</v>
       </c>
       <c r="C4" t="n">
-        <v>8069</v>
+        <v>9621</v>
       </c>
       <c r="D4" t="n">
-        <v>10954</v>
+        <v>10507</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2237</v>
+        <v>2244</v>
       </c>
       <c r="C5" t="n">
-        <v>8443</v>
+        <v>9898</v>
       </c>
       <c r="D5" t="n">
-        <v>5311</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="C6" t="n">
-        <v>6465</v>
+        <v>7356</v>
       </c>
       <c r="D6" t="n">
-        <v>1678</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>3358</v>
+        <v>4191</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1549</v>
+        <v>2108</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>566</v>
+        <v>670</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2494</v>
+        <v>2630</v>
       </c>
       <c r="C2" t="n">
-        <v>4231</v>
+        <v>2870</v>
       </c>
       <c r="D2" t="n">
-        <v>11463</v>
+        <v>14048</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2786</v>
+        <v>2864</v>
       </c>
       <c r="C3" t="n">
-        <v>5471</v>
+        <v>5839</v>
       </c>
       <c r="D3" t="n">
-        <v>12783</v>
+        <v>14008</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2945</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>7392</v>
+        <v>8632</v>
       </c>
       <c r="D4" t="n">
-        <v>11033</v>
+        <v>10746</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2450</v>
+        <v>2408</v>
       </c>
       <c r="C5" t="n">
-        <v>8455</v>
+        <v>9979</v>
       </c>
       <c r="D5" t="n">
-        <v>5901</v>
+        <v>5162</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1318</v>
+        <v>1293</v>
       </c>
       <c r="C6" t="n">
-        <v>7345</v>
+        <v>8378</v>
       </c>
       <c r="D6" t="n">
-        <v>2004</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>4348</v>
+        <v>5118</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1996</v>
+        <v>2645</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>705</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3210</v>
+        <v>3607</v>
       </c>
       <c r="C2" t="n">
-        <v>6318</v>
+        <v>3806</v>
       </c>
       <c r="D2" t="n">
-        <v>17241</v>
+        <v>16099</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2257</v>
+        <v>2350</v>
       </c>
       <c r="C3" t="n">
-        <v>4430</v>
+        <v>4271</v>
       </c>
       <c r="D3" t="n">
-        <v>11806</v>
+        <v>13138</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2535</v>
+        <v>2555</v>
       </c>
       <c r="C4" t="n">
-        <v>6426</v>
+        <v>7353</v>
       </c>
       <c r="D4" t="n">
-        <v>10949</v>
+        <v>10857</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2390</v>
+        <v>2366</v>
       </c>
       <c r="C5" t="n">
-        <v>7850</v>
+        <v>9171</v>
       </c>
       <c r="D5" t="n">
-        <v>6411</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1578</v>
+        <v>1529</v>
       </c>
       <c r="C6" t="n">
-        <v>7709</v>
+        <v>8977</v>
       </c>
       <c r="D6" t="n">
-        <v>2464</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="C7" t="n">
-        <v>5462</v>
+        <v>6234</v>
       </c>
       <c r="D7" t="n">
-        <v>899</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>2844</v>
+        <v>3443</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1092</v>
+        <v>1300</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4763</v>
+        <v>6992</v>
       </c>
       <c r="C2" t="n">
-        <v>8323</v>
+        <v>14749</v>
       </c>
       <c r="D2" t="n">
-        <v>3914</v>
+        <v>5604</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2324</v>
+        <v>2665</v>
       </c>
       <c r="C2" t="n">
-        <v>3640</v>
+        <v>2254</v>
       </c>
       <c r="D2" t="n">
-        <v>12827</v>
+        <v>11977</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3000</v>
+        <v>3103</v>
       </c>
       <c r="C3" t="n">
-        <v>5242</v>
+        <v>4704</v>
       </c>
       <c r="D3" t="n">
-        <v>13035</v>
+        <v>14347</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3503</v>
+        <v>3492</v>
       </c>
       <c r="C4" t="n">
-        <v>9081</v>
+        <v>10327</v>
       </c>
       <c r="D4" t="n">
-        <v>11313</v>
+        <v>11011</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="C5" t="n">
-        <v>11168</v>
+        <v>13024</v>
       </c>
       <c r="D5" t="n">
-        <v>5823</v>
+        <v>5064</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="C6" t="n">
-        <v>6788</v>
+        <v>7604</v>
       </c>
       <c r="D6" t="n">
-        <v>1973</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>2787</v>
+        <v>3374</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1070</v>
+        <v>1274</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5644</v>
+        <v>8119</v>
       </c>
       <c r="C2" t="n">
-        <v>3646</v>
+        <v>7884</v>
       </c>
       <c r="D2" t="n">
-        <v>16617</v>
+        <v>7132</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2025</v>
+        <v>2970</v>
       </c>
       <c r="C3" t="n">
-        <v>4261</v>
+        <v>7433</v>
       </c>
       <c r="D3" t="n">
-        <v>1328</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4458</v>
+        <v>5316</v>
       </c>
       <c r="C2" t="n">
-        <v>3629</v>
+        <v>5941</v>
       </c>
       <c r="D2" t="n">
-        <v>17247</v>
+        <v>19241</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3148</v>
+        <v>4552</v>
       </c>
       <c r="C3" t="n">
-        <v>3403</v>
+        <v>6630</v>
       </c>
       <c r="D3" t="n">
-        <v>3798</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>913</v>
+        <v>1324</v>
       </c>
       <c r="C4" t="n">
-        <v>2539</v>
+        <v>4398</v>
       </c>
       <c r="D4" t="n">
-        <v>1448</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5065</v>
+        <v>6478</v>
       </c>
       <c r="C2" t="n">
-        <v>4011</v>
+        <v>7567</v>
       </c>
       <c r="D2" t="n">
-        <v>26835</v>
+        <v>25846</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3115</v>
+        <v>4100</v>
       </c>
       <c r="C3" t="n">
-        <v>3052</v>
+        <v>5429</v>
       </c>
       <c r="D3" t="n">
-        <v>5676</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1718</v>
+        <v>2459</v>
       </c>
       <c r="C4" t="n">
-        <v>2975</v>
+        <v>5549</v>
       </c>
       <c r="D4" t="n">
-        <v>1855</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>435</v>
+        <v>593</v>
       </c>
       <c r="C5" t="n">
-        <v>1482</v>
+        <v>2460</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6119</v>
+        <v>5607</v>
       </c>
       <c r="C2" t="n">
-        <v>6537</v>
+        <v>4455</v>
       </c>
       <c r="D2" t="n">
-        <v>29133</v>
+        <v>24068</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3311</v>
+        <v>4270</v>
       </c>
       <c r="C3" t="n">
-        <v>3088</v>
+        <v>5674</v>
       </c>
       <c r="D3" t="n">
-        <v>8492</v>
+        <v>7752</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>2780</v>
       </c>
       <c r="C4" t="n">
-        <v>2955</v>
+        <v>5370</v>
       </c>
       <c r="D4" t="n">
-        <v>2477</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>898</v>
+        <v>1234</v>
       </c>
       <c r="C5" t="n">
-        <v>2239</v>
+        <v>3956</v>
       </c>
       <c r="D5" t="n">
-        <v>1271</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>899</v>
+        <v>1376</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6375</v>
+        <v>6059</v>
       </c>
       <c r="C2" t="n">
-        <v>6147</v>
+        <v>8369</v>
       </c>
       <c r="D2" t="n">
-        <v>26888</v>
+        <v>23609</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3415</v>
+        <v>3569</v>
       </c>
       <c r="C3" t="n">
-        <v>3998</v>
+        <v>4199</v>
       </c>
       <c r="D3" t="n">
-        <v>10378</v>
+        <v>8990</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1670</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="n">
-        <v>2484</v>
+        <v>4479</v>
       </c>
       <c r="D4" t="n">
-        <v>3034</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>764</v>
+        <v>1043</v>
       </c>
       <c r="C5" t="n">
-        <v>1910</v>
+        <v>3406</v>
       </c>
       <c r="D5" t="n">
-        <v>1177</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>1055</v>
+        <v>1758</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>399</v>
+        <v>538</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5855</v>
+        <v>6675</v>
       </c>
       <c r="C2" t="n">
-        <v>9373</v>
+        <v>12331</v>
       </c>
       <c r="D2" t="n">
-        <v>23187</v>
+        <v>27659</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4092</v>
+        <v>3980</v>
       </c>
       <c r="C3" t="n">
-        <v>4528</v>
+        <v>5682</v>
       </c>
       <c r="D3" t="n">
-        <v>12503</v>
+        <v>10784</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2254</v>
+        <v>2500</v>
       </c>
       <c r="C4" t="n">
-        <v>3362</v>
+        <v>4219</v>
       </c>
       <c r="D4" t="n">
-        <v>4492</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1092</v>
+        <v>1420</v>
       </c>
       <c r="C5" t="n">
-        <v>2193</v>
+        <v>3953</v>
       </c>
       <c r="D5" t="n">
-        <v>1515</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>482</v>
+        <v>637</v>
       </c>
       <c r="C6" t="n">
-        <v>1542</v>
+        <v>2637</v>
       </c>
       <c r="D6" t="n">
-        <v>817</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>778</v>
+        <v>1219</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>320</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5228</v>
+        <v>5220</v>
       </c>
       <c r="C2" t="n">
-        <v>9587</v>
+        <v>9613</v>
       </c>
       <c r="D2" t="n">
-        <v>19305</v>
+        <v>29784</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4085</v>
+        <v>4326</v>
       </c>
       <c r="C3" t="n">
-        <v>6237</v>
+        <v>7968</v>
       </c>
       <c r="D3" t="n">
-        <v>13312</v>
+        <v>12589</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2722</v>
+        <v>2777</v>
       </c>
       <c r="C4" t="n">
-        <v>3963</v>
+        <v>4891</v>
       </c>
       <c r="D4" t="n">
-        <v>5850</v>
+        <v>4965</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1475</v>
+        <v>1701</v>
       </c>
       <c r="C5" t="n">
-        <v>2777</v>
+        <v>4013</v>
       </c>
       <c r="D5" t="n">
-        <v>2040</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>719</v>
+        <v>925</v>
       </c>
       <c r="C6" t="n">
-        <v>1880</v>
+        <v>3289</v>
       </c>
       <c r="D6" t="n">
-        <v>924</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>1189</v>
+        <v>1941</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>557</v>
+        <v>792</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_47_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6153</v>
+        <v>7096</v>
       </c>
       <c r="C2" t="n">
-        <v>5946</v>
+        <v>10049</v>
       </c>
       <c r="D2" t="n">
-        <v>23684</v>
+        <v>41316</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3901</v>
+        <v>4644</v>
       </c>
       <c r="C3" t="n">
-        <v>7670</v>
+        <v>7941</v>
       </c>
       <c r="D3" t="n">
-        <v>14198</v>
+        <v>19890</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2994</v>
+        <v>3279</v>
       </c>
       <c r="C4" t="n">
-        <v>6278</v>
+        <v>4942</v>
       </c>
       <c r="D4" t="n">
-        <v>6131</v>
+        <v>8484</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1921</v>
+        <v>2134</v>
       </c>
       <c r="C5" t="n">
-        <v>4359</v>
+        <v>4053</v>
       </c>
       <c r="D5" t="n">
-        <v>2222</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>1250</v>
       </c>
       <c r="C6" t="n">
-        <v>3563</v>
+        <v>3510</v>
       </c>
       <c r="D6" t="n">
-        <v>1011</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="C7" t="n">
-        <v>2574</v>
+        <v>2339</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C8" t="n">
-        <v>1301</v>
+        <v>1123</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7895</v>
+        <v>9749</v>
       </c>
       <c r="C2" t="n">
-        <v>15924</v>
+        <v>11537</v>
       </c>
       <c r="D2" t="n">
-        <v>20485</v>
+        <v>42337</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3963</v>
+        <v>4627</v>
       </c>
       <c r="C3" t="n">
-        <v>6112</v>
+        <v>7818</v>
       </c>
       <c r="D3" t="n">
-        <v>14480</v>
+        <v>21327</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2885</v>
+        <v>3275</v>
       </c>
       <c r="C4" t="n">
-        <v>6788</v>
+        <v>6192</v>
       </c>
       <c r="D4" t="n">
-        <v>7124</v>
+        <v>9978</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2113</v>
+        <v>2303</v>
       </c>
       <c r="C5" t="n">
-        <v>5073</v>
+        <v>4313</v>
       </c>
       <c r="D5" t="n">
-        <v>2754</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1340</v>
+        <v>1480</v>
       </c>
       <c r="C6" t="n">
-        <v>3838</v>
+        <v>3672</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>714</v>
+        <v>777</v>
       </c>
       <c r="C7" t="n">
-        <v>2999</v>
+        <v>2831</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="C8" t="n">
-        <v>1811</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>830</v>
+        <v>698</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>62</v>
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8125</v>
+        <v>9928</v>
       </c>
       <c r="C2" t="n">
-        <v>15851</v>
+        <v>11046</v>
       </c>
       <c r="D2" t="n">
-        <v>26543</v>
+        <v>47554</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4434</v>
+        <v>5292</v>
       </c>
       <c r="C3" t="n">
-        <v>8822</v>
+        <v>8229</v>
       </c>
       <c r="D3" t="n">
-        <v>14273</v>
+        <v>22349</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>3221</v>
       </c>
       <c r="C4" t="n">
-        <v>6302</v>
+        <v>6659</v>
       </c>
       <c r="D4" t="n">
-        <v>7966</v>
+        <v>11104</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2148</v>
+        <v>2374</v>
       </c>
       <c r="C5" t="n">
-        <v>5610</v>
+        <v>4921</v>
       </c>
       <c r="D5" t="n">
-        <v>3231</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1493</v>
+        <v>1632</v>
       </c>
       <c r="C6" t="n">
-        <v>4291</v>
+        <v>3887</v>
       </c>
       <c r="D6" t="n">
-        <v>1360</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>863</v>
+        <v>932</v>
       </c>
       <c r="C7" t="n">
-        <v>3289</v>
+        <v>3115</v>
       </c>
       <c r="D7" t="n">
-        <v>722</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="C8" t="n">
-        <v>2234</v>
+        <v>2030</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C9" t="n">
-        <v>1177</v>
+        <v>1009</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>511</v>
+        <v>430</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>41</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7528</v>
+        <v>9214</v>
       </c>
       <c r="C2" t="n">
-        <v>11032</v>
+        <v>7864</v>
       </c>
       <c r="D2" t="n">
-        <v>21919</v>
+        <v>39330</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5154</v>
+        <v>5990</v>
       </c>
       <c r="C3" t="n">
-        <v>12840</v>
+        <v>11812</v>
       </c>
       <c r="D3" t="n">
-        <v>15464</v>
+        <v>23685</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1984</v>
+        <v>2193</v>
       </c>
       <c r="C4" t="n">
-        <v>8713</v>
+        <v>8176</v>
       </c>
       <c r="D4" t="n">
-        <v>7433</v>
+        <v>10110</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1379</v>
+        <v>1507</v>
       </c>
       <c r="C5" t="n">
-        <v>4205</v>
+        <v>3809</v>
       </c>
       <c r="D5" t="n">
-        <v>2201</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>797</v>
+        <v>861</v>
       </c>
       <c r="C6" t="n">
-        <v>3223</v>
+        <v>3052</v>
       </c>
       <c r="D6" t="n">
-        <v>707</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="C7" t="n">
-        <v>2189</v>
+        <v>1989</v>
       </c>
       <c r="D7" t="n">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>988</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>500</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
         <v>158</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>62</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>40</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4602</v>
+        <v>5563</v>
       </c>
       <c r="C2" t="n">
-        <v>4718</v>
+        <v>3636</v>
       </c>
       <c r="D2" t="n">
-        <v>15892</v>
+        <v>27898</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5290</v>
+        <v>6271</v>
       </c>
       <c r="C3" t="n">
-        <v>10945</v>
+        <v>9206</v>
       </c>
       <c r="D3" t="n">
-        <v>15424</v>
+        <v>24361</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2733</v>
+        <v>3071</v>
       </c>
       <c r="C4" t="n">
-        <v>10728</v>
+        <v>9925</v>
       </c>
       <c r="D4" t="n">
-        <v>8506</v>
+        <v>11951</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1526</v>
+        <v>1669</v>
       </c>
       <c r="C5" t="n">
-        <v>6093</v>
+        <v>5589</v>
       </c>
       <c r="D5" t="n">
-        <v>2779</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>933</v>
+        <v>997</v>
       </c>
       <c r="C6" t="n">
-        <v>3709</v>
+        <v>3449</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>2644</v>
+        <v>2424</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>1473</v>
+        <v>1272</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>128</v>
@@ -2178,7 +2178,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>62</v>
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>60</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4384</v>
+        <v>5693</v>
       </c>
       <c r="C2" t="n">
-        <v>13248</v>
+        <v>10564</v>
       </c>
       <c r="D2" t="n">
-        <v>23099</v>
+        <v>25482</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4213</v>
+        <v>5039</v>
       </c>
       <c r="C3" t="n">
-        <v>7245</v>
+        <v>6020</v>
       </c>
       <c r="D3" t="n">
-        <v>14451</v>
+        <v>23438</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3269</v>
+        <v>3758</v>
       </c>
       <c r="C4" t="n">
-        <v>10606</v>
+        <v>9387</v>
       </c>
       <c r="D4" t="n">
-        <v>9376</v>
+        <v>13493</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>1959</v>
       </c>
       <c r="C5" t="n">
-        <v>8057</v>
+        <v>7387</v>
       </c>
       <c r="D5" t="n">
-        <v>3574</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1074</v>
+        <v>1169</v>
       </c>
       <c r="C6" t="n">
-        <v>4740</v>
+        <v>4355</v>
       </c>
       <c r="D6" t="n">
-        <v>1114</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="C7" t="n">
-        <v>3081</v>
+        <v>2834</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>1945</v>
+        <v>1724</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>886</v>
+        <v>738</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>47</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>22</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2672</v>
+        <v>3503</v>
       </c>
       <c r="C2" t="n">
-        <v>6403</v>
+        <v>5190</v>
       </c>
       <c r="D2" t="n">
-        <v>16107</v>
+        <v>18004</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4105</v>
+        <v>5005</v>
       </c>
       <c r="C3" t="n">
-        <v>8968</v>
+        <v>7283</v>
       </c>
       <c r="D3" t="n">
-        <v>15026</v>
+        <v>23146</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3580</v>
+        <v>4090</v>
       </c>
       <c r="C4" t="n">
-        <v>10371</v>
+        <v>9090</v>
       </c>
       <c r="D4" t="n">
-        <v>10048</v>
+        <v>14582</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1867</v>
+        <v>2020</v>
       </c>
       <c r="C5" t="n">
-        <v>9910</v>
+        <v>8932</v>
       </c>
       <c r="D5" t="n">
-        <v>3763</v>
+        <v>4752</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>873</v>
+        <v>943</v>
       </c>
       <c r="C6" t="n">
-        <v>5532</v>
+        <v>5111</v>
       </c>
       <c r="D6" t="n">
-        <v>1091</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>3346</v>
+        <v>3004</v>
       </c>
       <c r="D7" t="n">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1421</v>
+        <v>1213</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
         <v>97</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>21</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3792</v>
+        <v>3654</v>
       </c>
       <c r="C2" t="n">
-        <v>5142</v>
+        <v>11597</v>
       </c>
       <c r="D2" t="n">
-        <v>19348</v>
+        <v>14606</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3037</v>
+        <v>3779</v>
       </c>
       <c r="C3" t="n">
-        <v>7021</v>
+        <v>5726</v>
       </c>
       <c r="D3" t="n">
-        <v>14178</v>
+        <v>21191</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3307</v>
+        <v>3912</v>
       </c>
       <c r="C4" t="n">
-        <v>9621</v>
+        <v>8102</v>
       </c>
       <c r="D4" t="n">
-        <v>10507</v>
+        <v>15371</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2244</v>
+        <v>2475</v>
       </c>
       <c r="C5" t="n">
-        <v>9898</v>
+        <v>8898</v>
       </c>
       <c r="D5" t="n">
-        <v>4589</v>
+        <v>5928</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>1194</v>
       </c>
       <c r="C6" t="n">
-        <v>7356</v>
+        <v>6621</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>4191</v>
+        <v>3846</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>2108</v>
+        <v>1833</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>670</v>
+        <v>571</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
         <v>97</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>45</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>19</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2630</v>
+        <v>2613</v>
       </c>
       <c r="C2" t="n">
-        <v>2870</v>
+        <v>7052</v>
       </c>
       <c r="D2" t="n">
-        <v>14048</v>
+        <v>11804</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2864</v>
+        <v>3282</v>
       </c>
       <c r="C3" t="n">
-        <v>5839</v>
+        <v>7249</v>
       </c>
       <c r="D3" t="n">
-        <v>14008</v>
+        <v>19334</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>3567</v>
       </c>
       <c r="C4" t="n">
-        <v>8632</v>
+        <v>7277</v>
       </c>
       <c r="D4" t="n">
-        <v>10746</v>
+        <v>15925</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2408</v>
+        <v>2724</v>
       </c>
       <c r="C5" t="n">
-        <v>9979</v>
+        <v>8709</v>
       </c>
       <c r="D5" t="n">
-        <v>5162</v>
+        <v>6711</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1293</v>
+        <v>1363</v>
       </c>
       <c r="C6" t="n">
-        <v>8378</v>
+        <v>7538</v>
       </c>
       <c r="D6" t="n">
-        <v>1665</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
-        <v>5118</v>
+        <v>4706</v>
       </c>
       <c r="D7" t="n">
-        <v>670</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2645</v>
+        <v>2289</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>90</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3607</v>
+        <v>5342</v>
       </c>
       <c r="C2" t="n">
-        <v>3806</v>
+        <v>7259</v>
       </c>
       <c r="D2" t="n">
-        <v>16099</v>
+        <v>16810</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2350</v>
+        <v>2584</v>
       </c>
       <c r="C3" t="n">
-        <v>4271</v>
+        <v>6418</v>
       </c>
       <c r="D3" t="n">
-        <v>13138</v>
+        <v>17284</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2555</v>
+        <v>3019</v>
       </c>
       <c r="C4" t="n">
-        <v>7353</v>
+        <v>7114</v>
       </c>
       <c r="D4" t="n">
-        <v>10857</v>
+        <v>15899</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2366</v>
+        <v>2754</v>
       </c>
       <c r="C5" t="n">
-        <v>9171</v>
+        <v>7991</v>
       </c>
       <c r="D5" t="n">
-        <v>5701</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1529</v>
+        <v>1636</v>
       </c>
       <c r="C6" t="n">
-        <v>8977</v>
+        <v>7895</v>
       </c>
       <c r="D6" t="n">
-        <v>2030</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="C7" t="n">
-        <v>6234</v>
+        <v>5675</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>3443</v>
+        <v>3092</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1300</v>
+        <v>1099</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>17</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6992</v>
+        <v>9775</v>
       </c>
       <c r="C2" t="n">
-        <v>14749</v>
+        <v>9770</v>
       </c>
       <c r="D2" t="n">
-        <v>5604</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2665</v>
+        <v>3944</v>
       </c>
       <c r="C2" t="n">
-        <v>2254</v>
+        <v>4355</v>
       </c>
       <c r="D2" t="n">
-        <v>11977</v>
+        <v>12507</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3103</v>
+        <v>3572</v>
       </c>
       <c r="C3" t="n">
-        <v>4704</v>
+        <v>7318</v>
       </c>
       <c r="D3" t="n">
-        <v>14347</v>
+        <v>18755</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3492</v>
+        <v>4088</v>
       </c>
       <c r="C4" t="n">
-        <v>10327</v>
+        <v>9885</v>
       </c>
       <c r="D4" t="n">
-        <v>11011</v>
+        <v>15952</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1412</v>
+        <v>1511</v>
       </c>
       <c r="C5" t="n">
-        <v>13024</v>
+        <v>11331</v>
       </c>
       <c r="D5" t="n">
-        <v>5064</v>
+        <v>6684</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C6" t="n">
-        <v>7604</v>
+        <v>6876</v>
       </c>
       <c r="D6" t="n">
-        <v>1647</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>3374</v>
+        <v>3030</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1274</v>
+        <v>1077</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" t="n">
         <v>90</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
         <v>59</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>16</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8119</v>
+        <v>8239</v>
       </c>
       <c r="C2" t="n">
-        <v>7884</v>
+        <v>10390</v>
       </c>
       <c r="D2" t="n">
-        <v>7132</v>
+        <v>10831</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2970</v>
+        <v>4150</v>
       </c>
       <c r="C3" t="n">
-        <v>7433</v>
+        <v>4924</v>
       </c>
       <c r="D3" t="n">
-        <v>1580</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5316</v>
+        <v>5342</v>
       </c>
       <c r="C2" t="n">
-        <v>5941</v>
+        <v>7107</v>
       </c>
       <c r="D2" t="n">
-        <v>19241</v>
+        <v>17871</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4552</v>
+        <v>5094</v>
       </c>
       <c r="C3" t="n">
-        <v>6630</v>
+        <v>6913</v>
       </c>
       <c r="D3" t="n">
-        <v>2396</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1324</v>
+        <v>1837</v>
       </c>
       <c r="C4" t="n">
-        <v>4398</v>
+        <v>2929</v>
       </c>
       <c r="D4" t="n">
-        <v>1499</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6478</v>
+        <v>6293</v>
       </c>
       <c r="C2" t="n">
-        <v>7567</v>
+        <v>6590</v>
       </c>
       <c r="D2" t="n">
-        <v>25846</v>
+        <v>29822</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4100</v>
+        <v>4308</v>
       </c>
       <c r="C3" t="n">
-        <v>5429</v>
+        <v>6084</v>
       </c>
       <c r="D3" t="n">
-        <v>4918</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2459</v>
+        <v>2912</v>
       </c>
       <c r="C4" t="n">
-        <v>5549</v>
+        <v>5086</v>
       </c>
       <c r="D4" t="n">
-        <v>1625</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>593</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>2460</v>
+        <v>1671</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5238,7 +5238,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5607</v>
+        <v>6401</v>
       </c>
       <c r="C2" t="n">
-        <v>4455</v>
+        <v>5250</v>
       </c>
       <c r="D2" t="n">
-        <v>24068</v>
+        <v>32660</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4270</v>
+        <v>4297</v>
       </c>
       <c r="C3" t="n">
-        <v>5674</v>
+        <v>5527</v>
       </c>
       <c r="D3" t="n">
-        <v>7752</v>
+        <v>9141</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2780</v>
+        <v>3077</v>
       </c>
       <c r="C4" t="n">
-        <v>5370</v>
+        <v>5507</v>
       </c>
       <c r="D4" t="n">
-        <v>2176</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1234</v>
+        <v>1512</v>
       </c>
       <c r="C5" t="n">
-        <v>3956</v>
+        <v>3357</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>397</v>
       </c>
       <c r="C6" t="n">
-        <v>1376</v>
+        <v>983</v>
       </c>
       <c r="D6" t="n">
         <v>935</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
         <v>471</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>174</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6059</v>
+        <v>7775</v>
       </c>
       <c r="C2" t="n">
-        <v>8369</v>
+        <v>5897</v>
       </c>
       <c r="D2" t="n">
-        <v>23609</v>
+        <v>45069</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3569</v>
+        <v>3848</v>
       </c>
       <c r="C3" t="n">
-        <v>4199</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>8990</v>
+        <v>11179</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2159</v>
+        <v>2279</v>
       </c>
       <c r="C4" t="n">
-        <v>4479</v>
+        <v>4466</v>
       </c>
       <c r="D4" t="n">
-        <v>2661</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1043</v>
+        <v>1185</v>
       </c>
       <c r="C5" t="n">
-        <v>3406</v>
+        <v>3246</v>
       </c>
       <c r="D5" t="n">
-        <v>1104</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>1758</v>
+        <v>1428</v>
       </c>
       <c r="D6" t="n">
-        <v>741</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>538</v>
+        <v>418</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5840,7 +5840,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>221</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5899,7 +5899,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5983,7 +5983,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6675</v>
+        <v>6850</v>
       </c>
       <c r="C2" t="n">
-        <v>12331</v>
+        <v>8456</v>
       </c>
       <c r="D2" t="n">
-        <v>27659</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3980</v>
+        <v>4778</v>
       </c>
       <c r="C3" t="n">
-        <v>5682</v>
+        <v>4533</v>
       </c>
       <c r="D3" t="n">
-        <v>10784</v>
+        <v>16049</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2500</v>
+        <v>2642</v>
       </c>
       <c r="C4" t="n">
-        <v>4219</v>
+        <v>4305</v>
       </c>
       <c r="D4" t="n">
-        <v>3856</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1420</v>
+        <v>1540</v>
       </c>
       <c r="C5" t="n">
-        <v>3953</v>
+        <v>3881</v>
       </c>
       <c r="D5" t="n">
-        <v>1358</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>637</v>
+        <v>745</v>
       </c>
       <c r="C6" t="n">
-        <v>2637</v>
+        <v>2423</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>1219</v>
+        <v>972</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>391</v>
+        <v>325</v>
       </c>
       <c r="D8" t="n">
         <v>374</v>
@@ -6171,7 +6171,7 @@
         <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6207,10 +6207,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6227,7 +6227,7 @@
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5220</v>
+        <v>6820</v>
       </c>
       <c r="C2" t="n">
-        <v>9613</v>
+        <v>12747</v>
       </c>
       <c r="D2" t="n">
-        <v>29784</v>
+        <v>36879</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4326</v>
+        <v>4733</v>
       </c>
       <c r="C3" t="n">
-        <v>7968</v>
+        <v>5727</v>
       </c>
       <c r="D3" t="n">
-        <v>12589</v>
+        <v>18521</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>3128</v>
       </c>
       <c r="C4" t="n">
-        <v>4891</v>
+        <v>4340</v>
       </c>
       <c r="D4" t="n">
-        <v>4965</v>
+        <v>6632</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1701</v>
+        <v>1832</v>
       </c>
       <c r="C5" t="n">
-        <v>4013</v>
+        <v>4024</v>
       </c>
       <c r="D5" t="n">
-        <v>1772</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>1018</v>
       </c>
       <c r="C6" t="n">
-        <v>3289</v>
+        <v>3114</v>
       </c>
       <c r="D6" t="n">
-        <v>877</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="C7" t="n">
-        <v>1941</v>
+        <v>1711</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>792</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>

--- a/output/yearly_population_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_47_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7096</v>
+        <v>1511</v>
       </c>
       <c r="C2" t="n">
-        <v>10049</v>
+        <v>3444</v>
       </c>
       <c r="D2" t="n">
-        <v>41316</v>
+        <v>13214</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4644</v>
+        <v>2252</v>
       </c>
       <c r="C3" t="n">
-        <v>7941</v>
+        <v>8391</v>
       </c>
       <c r="D3" t="n">
-        <v>19890</v>
+        <v>11591</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3279</v>
+        <v>1507</v>
       </c>
       <c r="C4" t="n">
-        <v>4942</v>
+        <v>9380</v>
       </c>
       <c r="D4" t="n">
-        <v>8484</v>
+        <v>4994</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2134</v>
+        <v>803</v>
       </c>
       <c r="C5" t="n">
-        <v>4053</v>
+        <v>4919</v>
       </c>
       <c r="D5" t="n">
-        <v>2801</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1250</v>
+        <v>323</v>
       </c>
       <c r="C6" t="n">
-        <v>3510</v>
+        <v>1846</v>
       </c>
       <c r="D6" t="n">
-        <v>1121</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>612</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>2339</v>
+        <v>639</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1123</v>
+        <v>341</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9749</v>
+        <v>1556</v>
       </c>
       <c r="C2" t="n">
-        <v>11537</v>
+        <v>3523</v>
       </c>
       <c r="D2" t="n">
-        <v>42337</v>
+        <v>14348</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4627</v>
+        <v>1616</v>
       </c>
       <c r="C3" t="n">
-        <v>7818</v>
+        <v>5061</v>
       </c>
       <c r="D3" t="n">
-        <v>21327</v>
+        <v>11021</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3275</v>
+        <v>1614</v>
       </c>
       <c r="C4" t="n">
-        <v>6192</v>
+        <v>8643</v>
       </c>
       <c r="D4" t="n">
-        <v>9978</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2303</v>
+        <v>997</v>
       </c>
       <c r="C5" t="n">
-        <v>4313</v>
+        <v>7219</v>
       </c>
       <c r="D5" t="n">
-        <v>3507</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1480</v>
+        <v>484</v>
       </c>
       <c r="C6" t="n">
-        <v>3672</v>
+        <v>3378</v>
       </c>
       <c r="D6" t="n">
-        <v>1348</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>777</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>2831</v>
+        <v>1224</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1600</v>
+        <v>478</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>698</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9928</v>
+        <v>824</v>
       </c>
       <c r="C2" t="n">
-        <v>11046</v>
+        <v>1488</v>
       </c>
       <c r="D2" t="n">
-        <v>47554</v>
+        <v>9652</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5292</v>
+        <v>1538</v>
       </c>
       <c r="C3" t="n">
-        <v>8229</v>
+        <v>4219</v>
       </c>
       <c r="D3" t="n">
-        <v>22349</v>
+        <v>11252</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3221</v>
+        <v>1774</v>
       </c>
       <c r="C4" t="n">
-        <v>6659</v>
+        <v>7966</v>
       </c>
       <c r="D4" t="n">
-        <v>11104</v>
+        <v>6676</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2374</v>
+        <v>1015</v>
       </c>
       <c r="C5" t="n">
-        <v>4921</v>
+        <v>8491</v>
       </c>
       <c r="D5" t="n">
-        <v>4236</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1632</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
-        <v>3887</v>
+        <v>4396</v>
       </c>
       <c r="D6" t="n">
-        <v>1620</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>932</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3115</v>
+        <v>1175</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>438</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2030</v>
+        <v>477</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1009</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>430</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9214</v>
+        <v>1096</v>
       </c>
       <c r="C2" t="n">
-        <v>7864</v>
+        <v>3766</v>
       </c>
       <c r="D2" t="n">
-        <v>39330</v>
+        <v>12365</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5990</v>
+        <v>1037</v>
       </c>
       <c r="C3" t="n">
-        <v>11812</v>
+        <v>2489</v>
       </c>
       <c r="D3" t="n">
-        <v>23685</v>
+        <v>10324</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2193</v>
+        <v>1483</v>
       </c>
       <c r="C4" t="n">
-        <v>8176</v>
+        <v>5898</v>
       </c>
       <c r="D4" t="n">
-        <v>10110</v>
+        <v>7263</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1507</v>
+        <v>1204</v>
       </c>
       <c r="C5" t="n">
-        <v>3809</v>
+        <v>8133</v>
       </c>
       <c r="D5" t="n">
-        <v>2685</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>861</v>
+        <v>577</v>
       </c>
       <c r="C6" t="n">
-        <v>3052</v>
+        <v>6363</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>404</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>1989</v>
+        <v>2618</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>988</v>
+        <v>766</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5563</v>
+        <v>565</v>
       </c>
       <c r="C2" t="n">
-        <v>3636</v>
+        <v>2074</v>
       </c>
       <c r="D2" t="n">
-        <v>27898</v>
+        <v>9570</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6271</v>
+        <v>925</v>
       </c>
       <c r="C3" t="n">
-        <v>9206</v>
+        <v>2779</v>
       </c>
       <c r="D3" t="n">
-        <v>24361</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3071</v>
+        <v>1231</v>
       </c>
       <c r="C4" t="n">
-        <v>9925</v>
+        <v>4374</v>
       </c>
       <c r="D4" t="n">
-        <v>11951</v>
+        <v>7651</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1669</v>
+        <v>1264</v>
       </c>
       <c r="C5" t="n">
-        <v>5589</v>
+        <v>7353</v>
       </c>
       <c r="D5" t="n">
-        <v>3510</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>997</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>3449</v>
+        <v>7253</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>2424</v>
+        <v>3897</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1272</v>
+        <v>1225</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5693</v>
+        <v>1419</v>
       </c>
       <c r="C2" t="n">
-        <v>10564</v>
+        <v>7861</v>
       </c>
       <c r="D2" t="n">
-        <v>25482</v>
+        <v>13270</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5039</v>
+        <v>654</v>
       </c>
       <c r="C3" t="n">
-        <v>6020</v>
+        <v>2163</v>
       </c>
       <c r="D3" t="n">
-        <v>23438</v>
+        <v>9274</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3758</v>
+        <v>973</v>
       </c>
       <c r="C4" t="n">
-        <v>9387</v>
+        <v>3517</v>
       </c>
       <c r="D4" t="n">
-        <v>13493</v>
+        <v>7802</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1959</v>
+        <v>1157</v>
       </c>
       <c r="C5" t="n">
-        <v>7387</v>
+        <v>5897</v>
       </c>
       <c r="D5" t="n">
-        <v>4618</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1169</v>
+        <v>849</v>
       </c>
       <c r="C6" t="n">
-        <v>4355</v>
+        <v>7228</v>
       </c>
       <c r="D6" t="n">
-        <v>1264</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>2834</v>
+        <v>5347</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1724</v>
+        <v>2271</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3503</v>
+        <v>953</v>
       </c>
       <c r="C2" t="n">
-        <v>5190</v>
+        <v>4151</v>
       </c>
       <c r="D2" t="n">
-        <v>18004</v>
+        <v>9554</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5005</v>
+        <v>1012</v>
       </c>
       <c r="C3" t="n">
-        <v>7283</v>
+        <v>3882</v>
       </c>
       <c r="D3" t="n">
-        <v>23146</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4090</v>
+        <v>1549</v>
       </c>
       <c r="C4" t="n">
-        <v>9090</v>
+        <v>5237</v>
       </c>
       <c r="D4" t="n">
-        <v>14582</v>
+        <v>8024</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2020</v>
+        <v>859</v>
       </c>
       <c r="C5" t="n">
-        <v>8932</v>
+        <v>9445</v>
       </c>
       <c r="D5" t="n">
-        <v>4752</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>943</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>5111</v>
+        <v>7010</v>
       </c>
       <c r="D6" t="n">
-        <v>1230</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>3004</v>
+        <v>2225</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1213</v>
+        <v>717</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3654</v>
+        <v>476</v>
       </c>
       <c r="C2" t="n">
-        <v>11597</v>
+        <v>2119</v>
       </c>
       <c r="D2" t="n">
-        <v>14606</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3779</v>
+        <v>829</v>
       </c>
       <c r="C3" t="n">
-        <v>5726</v>
+        <v>3535</v>
       </c>
       <c r="D3" t="n">
-        <v>21191</v>
+        <v>9484</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3912</v>
+        <v>1079</v>
       </c>
       <c r="C4" t="n">
-        <v>8102</v>
+        <v>4311</v>
       </c>
       <c r="D4" t="n">
-        <v>15371</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2475</v>
+        <v>818</v>
       </c>
       <c r="C5" t="n">
-        <v>8898</v>
+        <v>6562</v>
       </c>
       <c r="D5" t="n">
-        <v>5928</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1194</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>6621</v>
+        <v>6694</v>
       </c>
       <c r="D6" t="n">
-        <v>1653</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3846</v>
+        <v>3056</v>
       </c>
       <c r="D7" t="n">
-        <v>630</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1833</v>
+        <v>841</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2613</v>
+        <v>302</v>
       </c>
       <c r="C2" t="n">
-        <v>7052</v>
+        <v>5613</v>
       </c>
       <c r="D2" t="n">
-        <v>11804</v>
+        <v>6519</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3282</v>
+        <v>553</v>
       </c>
       <c r="C3" t="n">
-        <v>7249</v>
+        <v>2391</v>
       </c>
       <c r="D3" t="n">
-        <v>19334</v>
+        <v>8352</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3567</v>
+        <v>844</v>
       </c>
       <c r="C4" t="n">
-        <v>7277</v>
+        <v>3823</v>
       </c>
       <c r="D4" t="n">
-        <v>15925</v>
+        <v>7917</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2724</v>
+        <v>844</v>
       </c>
       <c r="C5" t="n">
-        <v>8709</v>
+        <v>5215</v>
       </c>
       <c r="D5" t="n">
-        <v>6711</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1363</v>
+        <v>491</v>
       </c>
       <c r="C6" t="n">
-        <v>7538</v>
+        <v>6616</v>
       </c>
       <c r="D6" t="n">
-        <v>1994</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>4706</v>
+        <v>4902</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>721</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>2289</v>
+        <v>1882</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>536</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5342</v>
+        <v>607</v>
       </c>
       <c r="C2" t="n">
-        <v>7259</v>
+        <v>12720</v>
       </c>
       <c r="D2" t="n">
-        <v>16810</v>
+        <v>11960</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2584</v>
+        <v>367</v>
       </c>
       <c r="C3" t="n">
-        <v>6418</v>
+        <v>3480</v>
       </c>
       <c r="D3" t="n">
-        <v>17284</v>
+        <v>7513</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3019</v>
+        <v>621</v>
       </c>
       <c r="C4" t="n">
-        <v>7114</v>
+        <v>3001</v>
       </c>
       <c r="D4" t="n">
-        <v>15899</v>
+        <v>7675</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2754</v>
+        <v>769</v>
       </c>
       <c r="C5" t="n">
-        <v>7991</v>
+        <v>4411</v>
       </c>
       <c r="D5" t="n">
-        <v>7656</v>
+        <v>5024</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1636</v>
+        <v>596</v>
       </c>
       <c r="C6" t="n">
-        <v>7895</v>
+        <v>5874</v>
       </c>
       <c r="D6" t="n">
-        <v>2492</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>545</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>5675</v>
+        <v>5706</v>
       </c>
       <c r="D7" t="n">
-        <v>856</v>
+        <v>896</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>3092</v>
+        <v>3242</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1099</v>
+        <v>1116</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9775</v>
+        <v>4714</v>
       </c>
       <c r="C2" t="n">
-        <v>9770</v>
+        <v>6726</v>
       </c>
       <c r="D2" t="n">
-        <v>13274</v>
+        <v>7763</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3944</v>
+        <v>435</v>
       </c>
       <c r="C2" t="n">
-        <v>4355</v>
+        <v>8894</v>
       </c>
       <c r="D2" t="n">
-        <v>12507</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3572</v>
+        <v>383</v>
       </c>
       <c r="C3" t="n">
-        <v>7318</v>
+        <v>6690</v>
       </c>
       <c r="D3" t="n">
-        <v>18755</v>
+        <v>7612</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4088</v>
+        <v>450</v>
       </c>
       <c r="C4" t="n">
-        <v>9885</v>
+        <v>3163</v>
       </c>
       <c r="D4" t="n">
-        <v>15952</v>
+        <v>7415</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1511</v>
+        <v>646</v>
       </c>
       <c r="C5" t="n">
-        <v>11331</v>
+        <v>3640</v>
       </c>
       <c r="D5" t="n">
-        <v>6684</v>
+        <v>5278</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>503</v>
+        <v>622</v>
       </c>
       <c r="C6" t="n">
-        <v>6876</v>
+        <v>5171</v>
       </c>
       <c r="D6" t="n">
-        <v>1934</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>3030</v>
+        <v>5776</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>1077</v>
+        <v>4223</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>1969</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>631</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8239</v>
+        <v>5993</v>
       </c>
       <c r="C2" t="n">
-        <v>10390</v>
+        <v>11089</v>
       </c>
       <c r="D2" t="n">
-        <v>10831</v>
+        <v>16757</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4150</v>
+        <v>1557</v>
       </c>
       <c r="C3" t="n">
-        <v>4924</v>
+        <v>2656</v>
       </c>
       <c r="D3" t="n">
-        <v>2869</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5342</v>
+        <v>3456</v>
       </c>
       <c r="C2" t="n">
-        <v>7107</v>
+        <v>5844</v>
       </c>
       <c r="D2" t="n">
-        <v>17871</v>
+        <v>14898</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5094</v>
+        <v>3199</v>
       </c>
       <c r="C3" t="n">
-        <v>6913</v>
+        <v>6658</v>
       </c>
       <c r="D3" t="n">
-        <v>3995</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1837</v>
+        <v>745</v>
       </c>
       <c r="C4" t="n">
-        <v>2929</v>
+        <v>1704</v>
       </c>
       <c r="D4" t="n">
-        <v>1759</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6293</v>
+        <v>2315</v>
       </c>
       <c r="C2" t="n">
-        <v>6590</v>
+        <v>3163</v>
       </c>
       <c r="D2" t="n">
-        <v>29822</v>
+        <v>15237</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4308</v>
+        <v>2745</v>
       </c>
       <c r="C3" t="n">
-        <v>6084</v>
+        <v>5374</v>
       </c>
       <c r="D3" t="n">
-        <v>5927</v>
+        <v>5693</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2912</v>
+        <v>1734</v>
       </c>
       <c r="C4" t="n">
-        <v>5086</v>
+        <v>4617</v>
       </c>
       <c r="D4" t="n">
-        <v>2134</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>799</v>
+        <v>364</v>
       </c>
       <c r="C5" t="n">
-        <v>1671</v>
+        <v>1064</v>
       </c>
       <c r="D5" t="n">
-        <v>1263</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6401</v>
+        <v>2459</v>
       </c>
       <c r="C2" t="n">
-        <v>5250</v>
+        <v>12533</v>
       </c>
       <c r="D2" t="n">
-        <v>32660</v>
+        <v>22504</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4297</v>
+        <v>2095</v>
       </c>
       <c r="C3" t="n">
-        <v>5527</v>
+        <v>3581</v>
       </c>
       <c r="D3" t="n">
-        <v>9141</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3077</v>
+        <v>1937</v>
       </c>
       <c r="C4" t="n">
-        <v>5507</v>
+        <v>4956</v>
       </c>
       <c r="D4" t="n">
-        <v>2760</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1512</v>
+        <v>890</v>
       </c>
       <c r="C5" t="n">
-        <v>3357</v>
+        <v>3020</v>
       </c>
       <c r="D5" t="n">
-        <v>1375</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>397</v>
+        <v>211</v>
       </c>
       <c r="C6" t="n">
-        <v>983</v>
+        <v>689</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7775</v>
+        <v>1746</v>
       </c>
       <c r="C2" t="n">
-        <v>5897</v>
+        <v>9453</v>
       </c>
       <c r="D2" t="n">
-        <v>45069</v>
+        <v>21631</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3848</v>
+        <v>1870</v>
       </c>
       <c r="C3" t="n">
-        <v>4423</v>
+        <v>7227</v>
       </c>
       <c r="D3" t="n">
-        <v>11179</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2279</v>
+        <v>1746</v>
       </c>
       <c r="C4" t="n">
-        <v>4466</v>
+        <v>4066</v>
       </c>
       <c r="D4" t="n">
-        <v>3270</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="C5" t="n">
-        <v>3246</v>
+        <v>3979</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>1428</v>
+        <v>1867</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>418</v>
+        <v>491</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6850</v>
+        <v>3261</v>
       </c>
       <c r="C2" t="n">
-        <v>8456</v>
+        <v>12374</v>
       </c>
       <c r="D2" t="n">
-        <v>39750</v>
+        <v>23155</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4778</v>
+        <v>1506</v>
       </c>
       <c r="C3" t="n">
-        <v>4533</v>
+        <v>7268</v>
       </c>
       <c r="D3" t="n">
-        <v>16049</v>
+        <v>9976</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2642</v>
+        <v>1548</v>
       </c>
       <c r="C4" t="n">
-        <v>4305</v>
+        <v>5589</v>
       </c>
       <c r="D4" t="n">
-        <v>4765</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1540</v>
+        <v>1295</v>
       </c>
       <c r="C5" t="n">
-        <v>3881</v>
+        <v>3900</v>
       </c>
       <c r="D5" t="n">
-        <v>1605</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>745</v>
+        <v>718</v>
       </c>
       <c r="C6" t="n">
-        <v>2423</v>
+        <v>2861</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>972</v>
+        <v>1138</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>325</v>
+        <v>383</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6820</v>
+        <v>2852</v>
       </c>
       <c r="C2" t="n">
-        <v>12747</v>
+        <v>7622</v>
       </c>
       <c r="D2" t="n">
-        <v>36879</v>
+        <v>18159</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4733</v>
+        <v>2358</v>
       </c>
       <c r="C3" t="n">
-        <v>5727</v>
+        <v>11132</v>
       </c>
       <c r="D3" t="n">
-        <v>18521</v>
+        <v>11084</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3128</v>
+        <v>1196</v>
       </c>
       <c r="C4" t="n">
-        <v>4340</v>
+        <v>7231</v>
       </c>
       <c r="D4" t="n">
-        <v>6632</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1832</v>
+        <v>663</v>
       </c>
       <c r="C5" t="n">
-        <v>4024</v>
+        <v>2803</v>
       </c>
       <c r="D5" t="n">
-        <v>2132</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>3114</v>
+        <v>1115</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>1711</v>
+        <v>375</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>641</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
